--- a/tests/realSuite/VOLLEY-S4_IC_Piano-viaggi_19-novembre-2025-def/input.xlsx
+++ b/tests/realSuite/VOLLEY-S4_IC_Piano-viaggi_19-novembre-2025-def/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,52 +501,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IC Lavarone, fraz. Gionghi 107/6</t>
+          <t>Folgaria, Park Palaghiaccio</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC FONDO REVO'</t>
+          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fermata Bus davanti VFF, Revò</t>
+          <t>IC Lavarone, fraz. Gionghi 107/6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC FONDO REVO'</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Via San Giovanni Bosco 14 Comano Terme</t>
+          <t>fermata Bus davanti VFF, Revò</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viale della Vittoria 43 - Rovereto</t>
+          <t>Via San Giovanni Bosco 14 Comano Terme</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Piazza S Vito, 1 - Andalo</t>
+          <t>Viale della Vittoria 43 - Rovereto</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,57 +571,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC MORI</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Via Giovanni XXIII, 64, Mori</t>
+          <t>Piazza S Vito, 1 - Andalo</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pergine - Scuola Media C. Andreatta, Via dei Caduti 39</t>
+          <t>Via Trento (fermata bus) - Spormaggiore</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC MORI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fermata Bus USL, Via Roma 2 Loc. Tonadico</t>
+          <t>Via Giovanni XXIII, 64, Mori</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
+          <t>Pergine - Scuola Media C. Andreatta, Via dei Caduti 39</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Riva del Garda, Via delle Ginestre Centro Sportivo Malossini</t>
+          <t>Fermata Bus USL, Via Roma 2 Loc. Tonadico</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,12 +646,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Piazzale Orsi, Fermata corriere davanti scuola IPIA - Rovereto</t>
+          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -661,12 +661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Via Livenza 1 – Rovereto</t>
+          <t>Riva del Garda, Via delle Ginestre Centro Sportivo Malossini</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,12 +676,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa – Coredo</t>
+          <t>Piazzale Orsi, Fermata corriere davanti scuola IPIA - Rovereto</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,27 +691,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Via Circonvalazione 44, Tione</t>
+          <t>Via Benacense, 27 - Rovereto</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trento, Fermata autobus Via Vittorio V.to</t>
+          <t>Via Livenza 1 – Rovereto</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,16 +721,106 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>IC TAIO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Piazza della Chiesa – Coredo</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IC TAIO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Piazza della Chiesa – Taio</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IC TIONE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Via Circonvalazione 44, Tione</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IC TRENTO 3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Trento, Fermata autobus Via Vittorio V.to</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>IC VALLE LAGHI</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Cavedine, P.zza Italia</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>9</v>
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IC VALLE LAGHI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vezzano, Via Roma 3 (fermata Farmacia)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IS MAFFEI di RIVA (students staff)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tests/realSuite/VOLLEY-S4_IC_Piano-viaggi_19-novembre-2025-def/input.xlsx
+++ b/tests/realSuite/VOLLEY-S4_IC_Piano-viaggi_19-novembre-2025-def/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,27 +436,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC ALTA VALLAGARINA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mattarello - Fermata bus "Al Parco", Via Torre Franca</t>
+          <t>Andata: P.le Orsi – Rovereto / Ritorno: Besenello, Calliano, Volano e poi P.le Orsi - Rovereto</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALTA VALLAGARINA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Andata: P.le Orsi – Rovereto / Ritorno: Besenello, Calliano, Volano e poi P.le Orsi - Rovereto</t>
+          <t>Via Fiera 1 loc. Creto Pieve di Bono</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,27 +466,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ARCO</t>
+          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arco, via Caproni Maini 28</t>
+          <t>Folgaria, Park Palaghiaccio</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via Fiera 1 loc. Creto Pieve di Bono</t>
+          <t>IC Lavarone, fraz. Gionghi 107/6</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,27 +496,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
+          <t>IC FONDO REVO'</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Folgaria, Park Palaghiaccio</t>
+          <t>fermata Bus davanti VFF, Revò</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC FOLGARIA – LAVARONE - LUSERNA</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IC Lavarone, fraz. Gionghi 107/6</t>
+          <t>Via San Giovanni Bosco 14 Comano Terme</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,27 +526,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC FONDO REVO'</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fermata Bus davanti VFF, Revò</t>
+          <t>Viale della Vittoria 43 - Rovereto</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via San Giovanni Bosco 14 Comano Terme</t>
+          <t>Piazza S Vito, 1 - Andalo</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,72 +556,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viale della Vittoria 43 - Rovereto</t>
+          <t>Via Trento (fermata bus) - Spormaggiore</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC MORI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Piazza S Vito, 1 - Andalo</t>
+          <t>Via Giovanni XXIII, 64, Mori</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Via Trento (fermata bus) - Spormaggiore</t>
+          <t>Pergine - Scuola Media C. Andreatta, Via dei Caduti 39</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC MORI</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Giovanni XXIII, 64, Mori</t>
+          <t>Fermata Bus USL, Via Roma 2 Loc. Tonadico</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pergine - Scuola Media C. Andreatta, Via dei Caduti 39</t>
+          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fermata Bus USL, Via Roma 2 Loc. Tonadico</t>
+          <t>Riva del Garda, Via delle Ginestre Centro Sportivo Malossini</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,12 +646,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
+          <t>Piazzale Orsi, Fermata corriere davanti scuola IPIA - Rovereto</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -661,27 +661,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Riva del Garda, Via delle Ginestre Centro Sportivo Malossini</t>
+          <t>Via Benacense, 27 - Rovereto</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Piazzale Orsi, Fermata corriere davanti scuola IPIA - Rovereto</t>
+          <t>Via Livenza 1 – Rovereto</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,42 +691,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Via Benacense, 27 - Rovereto</t>
+          <t>Piazza della Chiesa – Coredo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Via Livenza 1 – Rovereto</t>
+          <t>Piazza della Chiesa – Taio</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa – Coredo</t>
+          <t>Via Circonvalazione 44, Tione</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,27 +736,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa – Taio</t>
+          <t>Trento, Fermata autobus Via Vittorio V.to</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC VALLE LAGHI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Via Circonvalazione 44, Tione</t>
+          <t>Cavedine, P.zza Italia</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,60 +766,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC VALLE LAGHI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trento, Fermata autobus Via Vittorio V.to</t>
+          <t>Vezzano, Via Roma 3 (fermata Farmacia)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC VALLE LAGHI</t>
+          <t>IS MAFFEI di RIVA (students staff)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cavedine, P.zza Italia</t>
+          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>IC VALLE LAGHI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Vezzano, Via Roma 3 (fermata Farmacia)</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>IS MAFFEI di RIVA (students staff)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Fermata Bus davanti scuola, Viale Damiano Chiesa, Riva del Garda</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
         <v>14</v>
       </c>
     </row>
